--- a/Result/checksun_type/加油站.xlsx
+++ b/Result/checksun_type/加油站.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>57.02</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>57.13</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>59.07</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>59.07</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2192968.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4785461.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4785461.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>3573714.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>3650915.16</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>3650915.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-137813.642412792</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2192968</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2192968.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>57.0</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>57.16</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>59.16</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>59.16</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2216413.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5068126.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5068126.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>3839517.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>3618658.78</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>3618658.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>8210.960228929296</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2216413</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2216413.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>57.04</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>57.24</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>59.27</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>59.27</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>4079511.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>5103243.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>5103243.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>4290497.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>3586153.98</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>3586153.98</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>214012.3225660697</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>4079511</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>4079511.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>57.06</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>57.23</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>59.36</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>59.36</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>7525394.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4646774.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4646774</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>4216167.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>3540630.78</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>3540630.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>300753.3286703387</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>7525394</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>7525394.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>57.06</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>57.23</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>59.45</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>59.45</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>7913020.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>3356528.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>3356528.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>3770791.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>3401568.58</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>3401568.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>44726.1113667828</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>7913020</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>7913020.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>57.08</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>57.18</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>59.54</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>59.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3606296.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2361967.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2361967</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>3158833.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>3263441.3</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>3263441.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-364155.7744728243</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3606296</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3606296.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>57.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>57.21</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>59.64</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>59.64</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2391995.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>2610908.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>2610908.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>3090425.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>3198895.32</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>3198895.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-473832.4765839488</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2391995</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2391995.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>57.17999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>57.23</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>59.74</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>59.74</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1797165.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3477752.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>3477752</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>3034191.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>3161309.32</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>3161309.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-483487.2125789849</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1797165</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1797165.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>57.17999999999999</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>57.31</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>59.84</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>59.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1074167.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3785561.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>3785561.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>3127056.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>3319030.04</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>3319030.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-416280.5064083589</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1074167</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1074167.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>57.2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>59.93</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>59.93</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2940212.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>4185055.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>4185055</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>3307928.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>3316088.38</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>3316088.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-227939.6937928805</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2940212</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2940212.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>57.16</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>60.02</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>60.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4851002.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>3955700.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>3955700.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3216318.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>3261025.14</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>3261025.14</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-150674.0795638794</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4851002</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4851002.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>23.78</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>25.41</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>29.34</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>29.34</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>16957.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>40222.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>40222.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>36225.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>45656.8</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>45656.8</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-128.4773472536399</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>16957</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>16957.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>23.87</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>25.53</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>29.57</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>29.57</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>10423.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>39572.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>39572.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>35892.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>46468.32</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>46468.32</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>1770.564730552833</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>10423</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>10423.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>24.13</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>25.69</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>29.84</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>102963.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>46267.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>46267.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>36465.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>47816.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>47816</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>5120.318958470918</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>102963</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>102963.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>24.45</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>30.13</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>30.13</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>57096.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>33377.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>33377.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>30911.4</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>47578.84</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>47578.84</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-192.1863930200743</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>57096</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>57096.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>24.85</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>26.08</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>30.42</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>30.42</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>13673.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>28177.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>28177.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>27949.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>49600.04</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>49600.04</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-2860.29452397077</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>13673</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>13673.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>26.28</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>30.7</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>13707.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>32229.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>32229</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>28779.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>51045.7</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>51045.7</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-1917.259906615658</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>13707</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>13707.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>25.14</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>26.43</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>30.97</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>30.97</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>43899.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>32211.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>32211.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>30385.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>51985.82</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>51985.82</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-505.2368851578067</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>43899</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>43899.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>25.3</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>26.54</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>31.24</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>38512.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>26664.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>26664.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>28643.9</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>52289.92</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>52289.92</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-1704.874108605236</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>38512</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>38512.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>25.4</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>26.62</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>31.52</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>31.52</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>31095.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>28445.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>28445.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>28670.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>52688.62</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>52688.62</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-2780.574638222803</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>31095</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>31095.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>25.79</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>31.79</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>31.79</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>33932.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>27722.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>27722.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>28545.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>52783.48</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>52783.48</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-3423.304872025652</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>33932</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>33932.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>26.2</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>26.78</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>32.07</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32.07</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>13621.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>25329.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>25329.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>28136.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>52600.76</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>52600.76</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-4523.194317743099</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>13621</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>13621.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>53.4</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>50.95</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>45.16</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>45.16</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>554745012.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>737022951.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>737022951.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>722290026.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>432550164.52</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>432550164.52</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>18557581.47945392</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>554745012</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>554745012.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>54.06</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>50.7</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>44.93</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>44.93</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>788408172.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>744011853.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>744011853.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>820775940.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>425312179.22</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>425312179.22</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>39334024.154495</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>788408172</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>788408172.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>54.46</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>50.37</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>44.69</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>44.69</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>885806096.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>711136410.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>711136410</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>841633534.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>412172663.7</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>412172663.7</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>42574531.39903605</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>885806096</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>885806096.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>54.34</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>49.89</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>44.39</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>49.89</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>44.39</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>668271837.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>695306190.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>695306190.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>849322965.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>397683648.48</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>397683648.48</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>35247816.62698615</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>668271837</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>668271837.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>54.38</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>49.56</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>44.12</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>44.12</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>787883641.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>674083378.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>674083378.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>894526103.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>386410052.78</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>386410052.78</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>46829472.68023682</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>787883641</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>787883641.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>54.14</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>48.98</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>43.78</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>43.78</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>589689523.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>707557101.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>707557101.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>878560467.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>374087560.62</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>374087560.62</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>48886664.01772928</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>589689523</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>589689523.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>54.5</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>43.51</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>43.51</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>624030953.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>897540026.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>897540026.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>845078994.9</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>364870429.04</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>364870429.04</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>71314640.57065678</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>624030953</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>624030953.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>54.17999999999999</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>47.96</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>43.21</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>43.21</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>806655000.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>972130659.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>972130659.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>803973395.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>355409680.66</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>355409680.66</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>97128216.69731545</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>806655000</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>806655000.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>53.58</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>42.9</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>562157776.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1003339741.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1003339741</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>739586306.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>343255370.04</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>343255370.04</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>110969026.9604951</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>562157776</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>562157776.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>52.94</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>46.89</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>42.63</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>42.63</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>955252254.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1114968829.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1114968829</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>707036283.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>338029209.8</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>338029209.8</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>152974564.6593055</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>955252254</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>955252254.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>51.51000000000001</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>42.34</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>42.34</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>1539604151.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1049563834.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1049563834.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>636189079.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>324215240.94</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>324215240.94</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>165401832.8483452</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>1539604151</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>1539604151.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>13.59</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>14.2</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>746018.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>886803.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>886803.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1428362.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>928007.14</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>928007.14</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-43405.48138256627</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>746018</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>746018.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>13.6</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>14.22</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>14.22</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>566106.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1042475.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1042475.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1456718.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>948319.72</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>948319.72</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-13137.11027664901</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>566106</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>566106.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>13.62</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>14.24</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>14.24</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>881496.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1530610.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1530610.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1470295.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>950268.5</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>950268.5</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>49848.88809882733</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>881496</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>881496.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>13.7</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>14.26</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>14.26</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>780635.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1690790.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1690790</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1500639.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>946822.34</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>946822.34</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>104256.7826316927</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>780635</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>780635.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>13.82</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>14.05</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>14.28</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>14.28</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1459764.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>2002272.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>2002272.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1486944.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>975304.08</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>975304.08</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>189065.4254417969</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1459764</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1459764.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>13.9</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>14.08</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>14.31</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>14.31</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1524375.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1969921.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1969921</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1423276.2</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>1014037.46</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1014037.46</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>230704.4714047387</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1524375</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1524375.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>13.96</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>14.32</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>14.32</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>3006782.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1870962.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1870962</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>1369601.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>1001548.82</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>1001548.82</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>275026.7702302008</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>3006782</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>3006782.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,21 +18257,17 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>14.14</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
+      <c r="AM42" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="AO42" t="inlineStr">
         <is>
           <t>14.34</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
-      </c>
       <c r="AP42" t="inlineStr">
         <is>
           <t>-3.57</t>
@@ -18552,20 +18308,16 @@
           <t>1682394.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1409981.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1409981.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>1158133.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>970395.6</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>970395.6</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>169692.633901211</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>1682394</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>1682394.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>14.02</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>14.15</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>14.34</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>2338048.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>1310489.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>1310489.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>1044737.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>945118.18</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>945118.1800000001</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>155053.5593633249</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>2338048</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>2338048.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>13.99</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>14.15</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>14.35</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1298006.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>971616.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>971616.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>880389.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>917483.72</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>917483.72</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>58354.32576051191</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1298006</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1298006.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>14.0</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>14.16</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>14.35</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1029580.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>876631.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>876631.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>862752.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>908015.94</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>908015.9399999999</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>29561.55183647503</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1029580</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1029580.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>15.72</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>15.32</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>15.32</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>14932290.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>19709918.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>19709918</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>32439751.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>29271921.5</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>29271921.5</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-2598980.933891349</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>14932290</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>14932290.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>15.74</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>15.47</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>15.31</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>15.31</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>23626496.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>23636903.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>23636903.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>39781592.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>29594788.02</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>29594788.02</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-1750259.684757896</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>23626496</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>23626496.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>15.76</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>15.31</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>15.31</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>22426210.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>25304744.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>25304744.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>42488423.7</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>29492454.86</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>29492454.86</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-1406813.554397322</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>22426210</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>22426210.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>15.85</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>15.44</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>15.31</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>15.31</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>19606346.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>25083631.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>25083631.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>43625750.1</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>29292260.18</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>29292260.18</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-737330.8126537427</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>19606346</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>19606346.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>15.95</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>15.42</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>15.32</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>15.32</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>17958248.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>28233382.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>28233382.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>44028247.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>29119188.92</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>29119188.92</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>547534.6331461519</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>17958248</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>17958248.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>16.06</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>15.38</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>15.31</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>15.31</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>34567218.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>45169585.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>45169585.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>44266042.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>28900575.46</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>28900575.46</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>2540083.818819344</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>34567218</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>34567218.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>16.13</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>15.36</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>15.31</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>15.31</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>31965701.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>55926281.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>55926281.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>42531588.3</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>28462518.2</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>28462518.2</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>3516332.876251794</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>31965701</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>31965701.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>16.06</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>15.33</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>15.3</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>21320646.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>59672102.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>59672102.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>41952355.2</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>28046954.36</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>28046954.36</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>5064125.034146301</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>21320646</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>21320646.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>15.89</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>15.28</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>15.29</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>35355098.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>62167868.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>62167868.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>42993123.2</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>27806066.18</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>27806066.18</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>8234936.687061794</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>35355098</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>35355098.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>15.68</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>15.24</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>15.28</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>15.28</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>102639266.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>59823112.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>59823112.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>42354123.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>27399153.42</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>27399153.42</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>10966871.45240314</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>102639266</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>102639266.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>15.39</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>15.27</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>15.27</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>88350696.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>43362499.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>43362499.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>34237743.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>25587592.1</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>25587592.1</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>7268943.422447816</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>88350696</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>88350696.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
